--- a/transport/transport_data.xlsx
+++ b/transport/transport_data.xlsx
@@ -7095,12 +7095,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>CB2201CC</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>P2849EE</t>
+          <t>B7902TM</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
@@ -7110,10 +7105,10 @@
         <v>18000</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>7.944444444444445</v>
+        <v>8.444444444444443</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
@@ -7130,11 +7125,11 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>Plamen Svetoslavov</t>
+          <t>Vesela Nikolova</t>
         </is>
       </c>
       <c r="V82" s="4" t="n">
-        <v>46112.63315780093</v>
+        <v>46112.65841324074</v>
       </c>
       <c r="W82" t="inlineStr">
         <is>

--- a/transport/transport_data.xlsx
+++ b/transport/transport_data.xlsx
@@ -358,8 +358,8 @@
   <cols>
     <col width="23.28" customWidth="1" min="1" max="1"/>
     <col width="23.28" customWidth="1" min="2" max="2"/>
-    <col width="42.48" customWidth="1" min="3" max="3"/>
-    <col width="23.28" customWidth="1" min="4" max="4"/>
+    <col width="23.28" customWidth="1" min="3" max="3"/>
+    <col width="42.48" customWidth="1" min="4" max="4"/>
     <col width="23.28" customWidth="1" min="5" max="5"/>
     <col width="23.28" customWidth="1" min="6" max="6"/>
     <col width="23.28" customWidth="1" min="7" max="7"/>
@@ -381,6 +381,7 @@
     <col width="23.28" customWidth="1" min="23" max="23"/>
     <col width="23.28" customWidth="1" min="24" max="24"/>
     <col width="23.28" customWidth="1" min="25" max="25"/>
+    <col width="23.28" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.2" customHeight="1">
@@ -396,115 +397,120 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>ВЪЗЛОЖИТЕЛ</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>КУРС</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>МАРШРУТ_СНИМКА</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ПРЕВОЗВАЧ</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ШОФЬОР</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ВЛЕКАЧ</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ЦИСТЕРНА</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>КМ</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Л</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>€_ЦЕНА_ОБЩО</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>€_ЦЕНА_ЗА_1000</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ФАКТУРА_НОМЕР</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>СТАТУС_ФАКТУРА</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>ИНФОРМАЦИЯ</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ТОЛ_РАЗХОДИ</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>ЗАРЕДЕНО_ГОРИВО</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>ДРУГИ_РАЗХОДИ</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>СЪЗДАТЕЛ</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>СЪЗДАДЕНО_НА</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>ПРОМЯНА_ОТ</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>ПОСЛЕДЕН_ЪПДЕЙТ</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>ГОДИНА</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>МЕСЕЦ</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ДЕН</t>
         </is>
@@ -521,73 +527,78 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Русе-Тервел-Русе</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Р7826КН</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Р2530ЕЕ</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="J2" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="K2" s="2" t="n">
         <v>32000</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="L2" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="M2" s="3" t="n">
         <v>8.90625</v>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T2" s="4" t="n">
+      <c r="U2" s="4" t="n">
         <v>46049.32540670139</v>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Plamen Svetoslavov</t>
-        </is>
-      </c>
-      <c r="V2" s="4" t="n">
-        <v>46079.50242523148</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>46113.78351554398</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -604,73 +615,78 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Варна-Риш-Нефтохим</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="J3" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="K3" s="2" t="n">
         <v>19100</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="L3" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="M3" s="3" t="n">
         <v>12.56544502617801</v>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46049.69214929398</v>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Plamen Svetoslavov</t>
-        </is>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>46054.34961052083</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>46113.78353037037</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -687,73 +703,78 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Нефтохим-Варна-Добрич-Караплит-Подайва-Варна</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="J4" s="2" t="n">
         <v>420</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="K4" s="2" t="n">
         <v>31700</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="L4" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="M4" s="3" t="n">
         <v>12.61829652996845</v>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T4" s="4" t="n">
+      <c r="U4" s="4" t="n">
         <v>46049.69400770833</v>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>46049.69552314815</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>46113.78353037037</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -770,68 +791,73 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>Варна-Шабла-Варна</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="J5" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="K5" s="2" t="n">
         <v>18000</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="L5" s="2" t="n">
         <v>153</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="M5" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T5" s="4" t="n">
+      <c r="U5" s="4" t="n">
         <v>46050.65226671296</v>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>46050.65388618055</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>46113.78353037037</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -848,73 +874,78 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>Варна-НХК-Повеляново-Добрич-Русе</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Р7826КН</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Р2530ЕЕ</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="J6" s="2" t="n">
         <v>560</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="K6" s="2" t="n">
         <v>30000</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="L6" s="2" t="n">
         <v>532</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="M6" s="3" t="n">
         <v>17.73333333333333</v>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T6" s="4" t="n">
+      <c r="U6" s="4" t="n">
         <v>46051.46477383102</v>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V6" s="4" t="n">
-        <v>46051.46621637732</v>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>46113.78353037037</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>29</t>
         </is>
@@ -931,68 +962,73 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>Варна-Долни Чифлик-Стожер-Ген.Киселово-Повеляново-Варна</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="J7" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="K7" s="2" t="n">
         <v>21500</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="L7" s="2" t="n">
         <v>187</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="M7" s="3" t="n">
         <v>8.697674418604652</v>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T7" s="4" t="n">
+      <c r="U7" s="4" t="n">
         <v>46051.46624328704</v>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="n">
-        <v>46052.60112396991</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="n">
+        <v>46113.78353037037</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>29</t>
         </is>
@@ -1009,68 +1045,73 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>Варна-Варна</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="J8" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="K8" s="2" t="n">
         <v>14000</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="L8" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="M8" s="3" t="n">
         <v>1.857142857142857</v>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T8" s="4" t="n">
+      <c r="U8" s="4" t="n">
         <v>46052.60141983796</v>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="n">
-        <v>46052.60253890046</v>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="n">
+        <v>46113.7820728588</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -1087,73 +1128,81 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>Русе-Тервел-Карапелит-Русе</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Р7826КН</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Р2530ЕЕ</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="J9" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="K9" s="2" t="n">
         <v>32500</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>342</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>10.52307692307692</v>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>49.71</v>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T9" s="4" t="n">
+      <c r="U9" s="4" t="n">
         <v>46052.60277517361</v>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="n">
-        <v>46052.60476643519</v>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="n">
+        <v>46113.7820965162</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -1170,73 +1219,78 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>Варна-Стефан Караджа-Добрич-Варна</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="J10" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="K10" s="2" t="n">
         <v>31500</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="L10" s="2" t="n">
         <v>162</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="M10" s="3" t="n">
         <v>5.142857142857142</v>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T10" s="4" t="n">
+      <c r="U10" s="4" t="n">
         <v>46057.63509267361</v>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="n">
-        <v>46057.63855699074</v>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W10" s="4" t="n">
+        <v>46113.7820965162</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -1253,73 +1307,81 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>Варна-Плевен-Провадия-Длгопол-Златни Пясъци-Аспарухово-Варна</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="J11" s="2" t="n">
         <v>900</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="K11" s="2" t="n">
         <v>30000</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="L11" s="2" t="n">
         <v>855</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="M11" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T11" s="4" t="n">
+      <c r="U11" s="4" t="n">
         <v>46057.63875394676</v>
       </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="n">
-        <v>46057.64089135417</v>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="n">
+        <v>46113.7820965162</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -1336,73 +1398,78 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>Варна-Девня-Варна</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="J12" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="K12" s="2" t="n">
         <v>17000</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="L12" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="M12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T12" s="4" t="n">
+      <c r="U12" s="4" t="n">
         <v>46057.64150436343</v>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="n">
-        <v>46057.64271638889</v>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="n">
+        <v>46113.7820965162</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -1419,73 +1486,78 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>Русе-Варна-Русе</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>CB2201CC</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>P2849EE</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="J13" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="K13" s="2" t="n">
         <v>5000</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="L13" s="2" t="n">
         <v>380</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="M13" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T13" s="4" t="n">
+      <c r="U13" s="4" t="n">
         <v>46057.64289916667</v>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V13" s="4" t="n">
-        <v>46059.68004901621</v>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="n">
+        <v>46113.7820965162</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -1502,73 +1574,81 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>Русе-Тервел-Карапелит-Русе</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Р7826КН</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Р2530ЕЕ</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="J14" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="K14" s="2" t="n">
         <v>32000</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="L14" s="2" t="n">
         <v>342</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="M14" s="3" t="n">
         <v>10.6875</v>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>50.37</v>
+      </c>
+      <c r="T14" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T14" s="4" t="n">
+      <c r="U14" s="4" t="n">
         <v>46057.65787804398</v>
       </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="n">
-        <v>46057.65879645833</v>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="n">
+        <v>46113.7820965162</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -1585,73 +1665,78 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>Варна-Каблешково-Поморие-НХК</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="J15" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="K15" s="2" t="n">
         <v>14600</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="L15" s="2" t="n">
         <v>152</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="M15" s="3" t="n">
         <v>10.41095890410959</v>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T15" s="4" t="n">
+      <c r="U15" s="4" t="n">
         <v>46057.65900025463</v>
       </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V15" s="4" t="n">
-        <v>46057.66077089121</v>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="n">
+        <v>46113.7820965162</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -1668,73 +1753,78 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>Нефтохим-Добрич-Варна</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="J16" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="K16" s="2" t="n">
         <v>21000</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="L16" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="M16" s="3" t="n">
         <v>11.42857142857143</v>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T16" s="4" t="n">
+      <c r="U16" s="4" t="n">
         <v>46057.66085986111</v>
       </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="n">
-        <v>46058.69724981482</v>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="n">
+        <v>46113.7820965162</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -1751,68 +1841,73 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>ОФИС ПЛОВДИВ</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>Пловдив-горски извор-плодовитово-братя даскалови-пловдив</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>ТРАНС ОЙЛ ЕООД</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>ХРИСТО ТОДОРЕВ ЗЛАТЕВ</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>PB5393PX</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="J17" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="K17" s="2" t="n">
         <v>10700</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="L17" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="M17" s="3" t="n">
         <v>9.345794392523365</v>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
         <is>
           <t>Simeon Hadzhiev</t>
         </is>
       </c>
-      <c r="T17" s="4" t="n">
+      <c r="U17" s="4" t="n">
         <v>46058.36966240741</v>
       </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Simeon Hadzhiev</t>
-        </is>
-      </c>
-      <c r="V17" s="4" t="n">
-        <v>46058.37130049768</v>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="n">
+        <v>46113.78339811342</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>05</t>
         </is>
@@ -1829,68 +1924,73 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>ОФИС ПЛОВДИВ</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>пловдив-бошуля-пловдив</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>ТРАНС ОЙЛ ЕООД</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>ХРИСТО ТОДОРЕВ ЗЛАТЕВ</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>PB5393PX</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="J18" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="K18" s="2" t="n">
         <v>14000</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="L18" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="M18" s="3" t="n">
         <v>4.642857142857143</v>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
         <is>
           <t>Simeon Hadzhiev</t>
         </is>
       </c>
-      <c r="T18" s="4" t="n">
+      <c r="U18" s="4" t="n">
         <v>46058.77573209491</v>
       </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Simeon Hadzhiev</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="n">
-        <v>46058.77918289352</v>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W18" s="4" t="n">
+        <v>46113.78341417824</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>05</t>
         </is>
@@ -1907,68 +2007,73 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>ОФИС ПЛОВДИВ</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>софия-елин пелин-радомир-софия</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>СГ ОЙЛ ТРАНСПОРТ ЕООД</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>СВЕТОСЛАВ ЛЮБЕНОВ</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>CA5494KC</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="J19" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="K19" s="2" t="n">
         <v>12100</v>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="L19" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="M19" s="3" t="n">
         <v>10.74380165289256</v>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
         <is>
           <t>Simeon Hadzhiev</t>
         </is>
       </c>
-      <c r="T19" s="4" t="n">
+      <c r="U19" s="4" t="n">
         <v>46058.779626875</v>
       </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Simeon Hadzhiev</t>
-        </is>
-      </c>
-      <c r="V19" s="4" t="n">
-        <v>46058.78143416667</v>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W19" s="4" t="n">
+        <v>46113.78341417824</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>05</t>
         </is>
@@ -1985,78 +2090,83 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>Варна-Суворово-Варна</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>{'name': 'viber_image_2026-02-06_17-32-49-760.jpg', 'size': 185211, 'type': 'file', 'upload_time': '2026-02-06T15:33:22.822+00:00', 'url': 'https://cloud.seatable.io/workspace/73766/asset/9ebe8e8a-2c5f-44c3-afdf-b98ab8a88929/external-apps/files/2026-02/viber_image_2026-02-06_17-32-49-760.jpg'}</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>"СИ-ТРАНС БЪЛГАРИЯ"  ЕООД</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>ТОДОР ДИМИТРОВ ПОПОВ</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>В9261РА</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="J20" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="K20" s="2" t="n">
         <v>6500</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="L20" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="M20" s="3" t="n">
         <v>13.84615384615385</v>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
       <c r="O20" t="inlineStr">
         <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
           <t>1 евро на км за малък камион - иска фиксиран транспорт 90 евро - СУ Никола Вапцаров + КРЗ Одесос</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T20" s="4" t="n">
+      <c r="U20" s="4" t="n">
         <v>46059.68035722222</v>
       </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Plamen Svetoslavov</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="n">
-        <v>46059.9057671412</v>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W20" s="4" t="n">
+        <v>46113.7820965162</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>06</t>
         </is>
@@ -2073,65 +2183,70 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>ОФИС ПЛОВДИВ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>софия химойл</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>СГ ОЙЛ ТРАНСПОРТ ЕООД</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>СВЕТОСЛАВ ЛЮБЕНОВ</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>CA5494KC</t>
         </is>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="K21" s="2" t="n">
         <v>15000</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="L21" s="3" t="n">
         <v>76.69</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="M21" s="3" t="n">
         <v>5.112666666666667</v>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
         <is>
           <t>Simeon Hadzhiev</t>
         </is>
       </c>
-      <c r="T21" s="4" t="n">
+      <c r="U21" s="4" t="n">
         <v>46060.64085678241</v>
       </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Plamen Svetoslavov</t>
-        </is>
-      </c>
-      <c r="V21" s="4" t="n">
-        <v>46061.49062966435</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W21" s="4" t="n">
+        <v>46113.78341417824</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>07</t>
         </is>
@@ -2148,68 +2263,73 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>ОФИС ПЛОВДИВ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>пловдив-белозем-пловдив-скобелево-пловдив</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>ТРАНС ОЙЛ ЕООД</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>ХРИСТО ТОДОРЕВ ЗЛАТЕВ</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>PB5393PX</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="J22" s="2" t="n">
         <v>196</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="K22" s="2" t="n">
         <v>32000</v>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="L22" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="M22" s="3" t="n">
         <v>3.90625</v>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
         <is>
           <t>Simeon Hadzhiev</t>
         </is>
       </c>
-      <c r="T22" s="4" t="n">
+      <c r="U22" s="4" t="n">
         <v>46060.64487152778</v>
       </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Simeon Hadzhiev</t>
-        </is>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>46060.64946173611</v>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W22" s="4" t="n">
+        <v>46113.78341417824</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>07</t>
         </is>
@@ -2226,68 +2346,73 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>ОФИС ПЛОВДИВ</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>софия-монтана-софия</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>СГ ОЙЛ ТРАНСПОРТ ЕООД</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>СВЕТОСЛАВ ЛЮБЕНОВ</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>CA5494KC</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
+      <c r="J23" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="J23" s="2" t="n">
+      <c r="K23" s="2" t="n">
         <v>18100</v>
       </c>
-      <c r="K23" s="2" t="n">
+      <c r="L23" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="M23" s="3" t="n">
         <v>13.53591160220994</v>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
         <is>
           <t>Simeon Hadzhiev</t>
         </is>
       </c>
-      <c r="T23" s="4" t="n">
+      <c r="U23" s="4" t="n">
         <v>46060.65033337963</v>
       </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Simeon Hadzhiev</t>
-        </is>
-      </c>
-      <c r="V23" s="4" t="n">
-        <v>46060.65189035879</v>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="n">
+        <v>46113.78341417824</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>07</t>
         </is>
@@ -2304,73 +2429,81 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>Русе-Варна-Добрич-Русе</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Р7826КН</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Р2530ЕЕ</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="J24" s="2" t="n">
         <v>440</v>
       </c>
-      <c r="J24" s="2" t="n">
+      <c r="K24" s="2" t="n">
         <v>32000</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="L24" s="2" t="n">
         <v>418</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="M24" s="3" t="n">
         <v>13.0625</v>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="T24" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T24" s="4" t="n">
+      <c r="U24" s="4" t="n">
         <v>46062.62343696759</v>
       </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="n">
-        <v>46063.72561</v>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W24" s="4" t="n">
+        <v>46113.7820965162</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>09</t>
         </is>
@@ -2387,70 +2520,75 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>ОФИС ПЛОВДИВ</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>софия-никас (рудината)</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>СГ ОЙЛ ТРАНСПОРТ ЕООД</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>ГЕОРГИ ЧАВДАРОВ ЛЮБЕНОВ</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>CA5494KC</t>
         </is>
       </c>
-      <c r="J25" s="2" t="n">
+      <c r="K25" s="2" t="n">
         <v>2000</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="L25" s="3" t="n">
         <v>76.69</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="M25" s="3" t="n">
         <v>38.345</v>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
       <c r="O25" t="inlineStr">
         <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
           <t>градски курс</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>Simeon Hadzhiev</t>
         </is>
       </c>
-      <c r="T25" s="4" t="n">
+      <c r="U25" s="4" t="n">
         <v>46062.73412034722</v>
       </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Simeon Hadzhiev</t>
-        </is>
-      </c>
-      <c r="V25" s="4" t="n">
-        <v>46062.79670418982</v>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W25" s="4" t="n">
+        <v>46113.78341417824</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>09</t>
         </is>
@@ -2467,68 +2605,73 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>ОФИС ПЛОВДИВ</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>Пловдив-димитровград-гълъбово-харманли-пловдив</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>ТРАНС ОЙЛ ЕООД</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>ХРИСТО ТОДОРЕВ ЗЛАТЕВ</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>PB5393PX</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="J26" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="J26" s="2" t="n">
+      <c r="K26" s="2" t="n">
         <v>19100</v>
       </c>
-      <c r="K26" s="2" t="n">
+      <c r="L26" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="M26" s="3" t="n">
         <v>8.376963350785342</v>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
         <is>
           <t>Simeon Hadzhiev</t>
         </is>
       </c>
-      <c r="T26" s="4" t="n">
+      <c r="U26" s="4" t="n">
         <v>46062.73675445602</v>
       </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Simeon Hadzhiev</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>46062.7402524537</v>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W26" s="4" t="n">
+        <v>46113.78341417824</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>09</t>
         </is>
@@ -2545,73 +2688,81 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>Русе-Варна</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Р7826КН</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Р2530ЕЕ</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
+      <c r="J27" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="J27" s="2" t="n">
+      <c r="K27" s="2" t="n">
         <v>30000</v>
       </c>
-      <c r="K27" s="2" t="n">
+      <c r="L27" s="2" t="n">
         <v>209</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="M27" s="3" t="n">
         <v>6.966666666666667</v>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="T27" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T27" s="4" t="n">
+      <c r="U27" s="4" t="n">
         <v>46065.33498443287</v>
       </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V27" s="4" t="n">
-        <v>46065.33599603009</v>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W27" s="4" t="n">
+        <v>46113.7820965162</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2628,73 +2779,81 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>Варна-Добрич-Русе</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Р7826КН</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Р2530ЕЕ</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
+      <c r="J28" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="J28" s="2" t="n">
+      <c r="K28" s="2" t="n">
         <v>32000</v>
       </c>
-      <c r="K28" s="2" t="n">
+      <c r="L28" s="2" t="n">
         <v>247</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="M28" s="3" t="n">
         <v>7.71875</v>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>35.22</v>
+      </c>
+      <c r="T28" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T28" s="4" t="n">
+      <c r="U28" s="4" t="n">
         <v>46065.33859748843</v>
       </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>46065.33975950231</v>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W28" s="4" t="n">
+        <v>46113.7820965162</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2711,73 +2870,81 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>Русе-Тервел-Русе</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Р7826КН</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Р2530ЕЕ</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
+      <c r="J29" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="J29" s="2" t="n">
+      <c r="K29" s="2" t="n">
         <v>29000</v>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="L29" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="M29" s="3" t="n">
         <v>9.827586206896552</v>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>67.34</v>
+      </c>
+      <c r="T29" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T29" s="4" t="n">
+      <c r="U29" s="4" t="n">
         <v>46066.31745449074</v>
       </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V29" s="4" t="n">
-        <v>46066.318259375</v>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W29" s="4" t="n">
+        <v>46113.7820965162</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -2794,68 +2961,73 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>Варна-Повеляново-Варна</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
+      <c r="J30" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="J30" s="2" t="n">
+      <c r="K30" s="2" t="n">
         <v>3000</v>
       </c>
-      <c r="K30" s="5" t="n">
+      <c r="L30" s="5" t="n">
         <v>42.5</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="M30" s="3" t="n">
         <v>14.16666666666667</v>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T30" s="4" t="n">
+      <c r="U30" s="4" t="n">
         <v>46069.52798105324</v>
       </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>46069.53052725695</v>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W30" s="4" t="n">
+        <v>46113.78213268518</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -2872,73 +3044,78 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>Варна-Девня-Смолница-Варна</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
+      <c r="J31" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="J31" s="2" t="n">
+      <c r="K31" s="2" t="n">
         <v>36000</v>
       </c>
-      <c r="K31" s="5" t="n">
+      <c r="L31" s="5" t="n">
         <v>161.6</v>
       </c>
-      <c r="L31" s="3" t="n">
+      <c r="M31" s="3" t="n">
         <v>4.488888888888889</v>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T31" s="4" t="n">
+      <c r="U31" s="4" t="n">
         <v>46069.53245862269</v>
       </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V31" s="4" t="n">
-        <v>46069.53334458333</v>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W31" s="4" t="n">
+        <v>46113.78213268518</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -2955,68 +3132,73 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>Варна- Аспарухово-Варна</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
+      <c r="J32" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="J32" s="2" t="n">
+      <c r="K32" s="2" t="n">
         <v>35000</v>
       </c>
-      <c r="K32" s="2" t="n">
+      <c r="L32" s="2" t="n">
         <v>187</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="M32" s="3" t="n">
         <v>5.342857142857143</v>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T32" s="4" t="n">
+      <c r="U32" s="4" t="n">
         <v>46073.50795790509</v>
       </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>46073.51022939815</v>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W32" s="4" t="n">
+        <v>46113.78213268518</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -3033,73 +3215,78 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>Варна-Повеляново-Ген.Киселово-Добрич-Варна</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
+      <c r="J33" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="J33" s="2" t="n">
+      <c r="K33" s="2" t="n">
         <v>31700</v>
       </c>
-      <c r="K33" s="2" t="n">
+      <c r="L33" s="2" t="n">
         <v>152</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="M33" s="3" t="n">
         <v>4.794952681388013</v>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T33" s="4" t="n">
+      <c r="U33" s="4" t="n">
         <v>46073.51002537037</v>
       </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V33" s="4" t="n">
-        <v>46073.51220881945</v>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W33" s="4" t="n">
+        <v>46113.78213268518</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -3116,73 +3303,78 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>Русе-Тервел-Карапелит-Русе</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>CB2201CC</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>P2849EE</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
+      <c r="J34" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="J34" s="2" t="n">
+      <c r="K34" s="2" t="n">
         <v>31500</v>
       </c>
-      <c r="K34" s="2" t="n">
+      <c r="L34" s="2" t="n">
         <v>342</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="M34" s="3" t="n">
         <v>10.85714285714286</v>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T34" s="4" t="n">
+      <c r="U34" s="4" t="n">
         <v>46073.51232930556</v>
       </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>46073.51367869213</v>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W34" s="4" t="n">
+        <v>46113.78213268518</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -3199,73 +3391,78 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>варна</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>CB2201CC</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>P2849EE</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
+      <c r="J35" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="J35" s="2" t="n">
+      <c r="K35" s="2" t="n">
         <v>5000</v>
       </c>
-      <c r="K35" s="2" t="n">
+      <c r="L35" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="M35" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T35" s="4" t="n">
+      <c r="U35" s="4" t="n">
         <v>46076.68929261574</v>
       </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V35" s="4" t="n">
-        <v>46076.70348971065</v>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W35" s="4" t="n">
+        <v>46113.78213268518</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -3282,73 +3479,78 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>Варна-НХК-Добрич-Варна</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>CB2201CC</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>P2849EE</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
+      <c r="J36" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="J36" s="2" t="n">
+      <c r="K36" s="2" t="n">
         <v>31700</v>
       </c>
-      <c r="K36" s="2" t="n">
+      <c r="L36" s="2" t="n">
         <v>430</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="M36" s="3" t="n">
         <v>13.56466876971609</v>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T36" s="4" t="n">
+      <c r="U36" s="4" t="n">
         <v>46076.69832314815</v>
       </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>46076.70627694445</v>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W36" s="4" t="n">
+        <v>46113.78213268518</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -3365,73 +3567,78 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>Русе-Силистра-Караплит-Тервел-Кладенци-Русе</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Р7826КН</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Р2530ЕЕ</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
+      <c r="J37" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="J37" s="2" t="n">
+      <c r="K37" s="2" t="n">
         <v>32000</v>
       </c>
-      <c r="K37" s="2" t="n">
+      <c r="L37" s="2" t="n">
         <v>371</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="M37" s="3" t="n">
         <v>11.59375</v>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T37" s="4" t="n">
+      <c r="U37" s="4" t="n">
         <v>46078.60538027778</v>
       </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V37" s="4" t="n">
-        <v>46078.62862679398</v>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W37" s="4" t="n">
+        <v>46113.78213268518</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -3448,73 +3655,78 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>Варна-Повеляново-Варна</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>CB2201CC</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>P2849EE</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
+      <c r="J38" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="J38" s="2" t="n">
+      <c r="K38" s="2" t="n">
         <v>27000</v>
       </c>
-      <c r="K38" s="2" t="n">
+      <c r="L38" s="2" t="n">
         <v>162</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="M38" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T38" s="4" t="n">
+      <c r="U38" s="4" t="n">
         <v>46078.62877524306</v>
       </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Plamen Svetoslavov</t>
-        </is>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>46079.54256951389</v>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W38" s="4" t="n">
+        <v>46113.78213268518</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -3531,73 +3743,78 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>Варна-Нефтохим-Добрич-Малина-Варна</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>CB2201CC</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>P2849EE</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
+      <c r="J39" s="2" t="n">
         <v>430</v>
       </c>
-      <c r="J39" s="2" t="n">
+      <c r="K39" s="2" t="n">
         <v>30000</v>
       </c>
-      <c r="K39" s="2" t="n">
+      <c r="L39" s="2" t="n">
         <v>410</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="M39" s="3" t="n">
         <v>13.66666666666667</v>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T39" s="4" t="n">
+      <c r="U39" s="4" t="n">
         <v>46085.68958916666</v>
       </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V39" s="4" t="n">
-        <v>46085.69251657408</v>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W39" s="4" t="n">
+        <v>46113.78213268518</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -3614,73 +3831,78 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>Варна-Карапелит-Тервел-Кипра-Варна</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>CB2201CC</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>P2849EE</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
+      <c r="J40" s="2" t="n">
         <v>490</v>
       </c>
-      <c r="J40" s="2" t="n">
+      <c r="K40" s="2" t="n">
         <v>32000</v>
       </c>
-      <c r="K40" s="2" t="n">
+      <c r="L40" s="2" t="n">
         <v>470</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="M40" s="3" t="n">
         <v>14.6875</v>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T40" s="4" t="n">
+      <c r="U40" s="4" t="n">
         <v>46085.69323543982</v>
       </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>46085.69449329861</v>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W40" s="4" t="n">
+        <v>46113.78188707176</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -3697,73 +3919,78 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>Варна-Девня-Ботево-Смолница-Добрич-Варна</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>CB2201CC</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>P2849EE</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
+      <c r="J41" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="J41" s="2" t="n">
+      <c r="K41" s="2" t="n">
         <v>32300</v>
       </c>
-      <c r="K41" s="2" t="n">
+      <c r="L41" s="2" t="n">
         <v>181</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="M41" s="3" t="n">
         <v>5.603715170278638</v>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T41" s="4" t="n">
+      <c r="U41" s="4" t="n">
         <v>46085.69483305555</v>
       </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V41" s="4" t="n">
-        <v>46085.69791484954</v>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W41" s="4" t="n">
+        <v>46113.78193960648</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -3780,68 +4007,73 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>Варна-Аспарухов-Ген.Тошево-Варна</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>ТРАНС ОЙЛ ЕООД</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>B7902TM</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
+      <c r="J42" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="J42" s="2" t="n">
+      <c r="K42" s="2" t="n">
         <v>17000</v>
       </c>
-      <c r="K42" s="2" t="n">
+      <c r="L42" s="2" t="n">
         <v>171</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="M42" s="3" t="n">
         <v>10.05882352941176</v>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T42" s="4" t="n">
+      <c r="U42" s="4" t="n">
         <v>46085.69801541667</v>
       </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V42" s="4" t="n">
-        <v>46086.60675380787</v>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W42" s="4" t="n">
+        <v>46113.78193960648</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -3858,68 +4090,73 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>НХК-Невестино-Риш-Нова Бяла Река-НХК</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>ДИРОСИ ООД</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>А1535ВВ</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
+      <c r="J43" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="J43" s="2" t="n">
+      <c r="K43" s="2" t="n">
         <v>13000</v>
       </c>
-      <c r="K43" s="2" t="n">
+      <c r="L43" s="2" t="n">
         <v>195</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="M43" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T43" s="4" t="n">
+      <c r="U43" s="4" t="n">
         <v>46085.69988991898</v>
       </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V43" s="4" t="n">
-        <v>46085.70354762732</v>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W43" s="4" t="n">
+        <v>46113.78193960648</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -3936,73 +4173,78 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>Варна-Каварна-Варна</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>CB2201CC</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>P2849EE</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
+      <c r="J44" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="J44" s="2" t="n">
+      <c r="K44" s="2" t="n">
         <v>25000</v>
       </c>
-      <c r="K44" s="2" t="n">
+      <c r="L44" s="2" t="n">
         <v>133</v>
       </c>
-      <c r="L44" s="3" t="n">
+      <c r="M44" s="3" t="n">
         <v>5.32</v>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T44" s="4" t="n">
+      <c r="U44" s="4" t="n">
         <v>46085.70368002315</v>
       </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V44" s="4" t="n">
-        <v>46085.70488208333</v>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W44" s="4" t="n">
+        <v>46113.78193960648</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -4019,73 +4261,78 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t>Варна-Вълчи дол-Доброплодно-Енево-Снежина-Блъсково-Варна</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>CB2201CC</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>P2849EE</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
+      <c r="J45" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="J45" s="2" t="n">
+      <c r="K45" s="2" t="n">
         <v>35000</v>
       </c>
-      <c r="K45" s="2" t="n">
+      <c r="L45" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="M45" s="3" t="n">
         <v>6.285714285714286</v>
       </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T45" s="4" t="n">
+      <c r="U45" s="4" t="n">
         <v>46085.70492685185</v>
       </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V45" s="4" t="n">
-        <v>46085.70756719908</v>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W45" s="4" t="n">
+        <v>46113.78193960648</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -4102,73 +4349,78 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>Варна-Сенокос-Добрич-Черна-Северняк-Кладенци-Тервел-Жегларци-Ведрина-Варна</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>CB2201CC</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>P2849EE</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
+      <c r="J46" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="J46" s="2" t="n">
+      <c r="K46" s="2" t="n">
         <v>33600</v>
       </c>
-      <c r="K46" s="2" t="n">
+      <c r="L46" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="L46" s="3" t="n">
+      <c r="M46" s="3" t="n">
         <v>9.523809523809526</v>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T46" s="4" t="n">
+      <c r="U46" s="4" t="n">
         <v>46085.70889583333</v>
       </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>46085.72144167824</v>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W46" s="4" t="n">
+        <v>46113.78193960648</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -4185,73 +4437,78 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>София-Орешец-Кула-София</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>ГРАНД  ПЕТРОЛ ЕООД</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>ДАНАИЛ ДОНКОВ</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>СВ7379ТС</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
+      <c r="J47" s="2" t="n">
         <v>420</v>
       </c>
-      <c r="J47" s="2" t="n">
+      <c r="K47" s="2" t="n">
         <v>26000</v>
       </c>
-      <c r="K47" s="2" t="n">
+      <c r="L47" s="2" t="n">
         <v>460</v>
       </c>
-      <c r="L47" s="3" t="n">
+      <c r="M47" s="3" t="n">
         <v>17.69230769230769</v>
       </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
       <c r="O47" t="inlineStr">
         <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
           <t>транспорт на км 1,10евро без ДДС</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T47" s="4" t="n">
+      <c r="U47" s="4" t="n">
         <v>46085.70898615741</v>
       </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V47" s="4" t="n">
-        <v>46085.71429056713</v>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W47" s="4" t="n">
+        <v>46113.78193960648</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -4268,68 +4525,73 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
           <t>НХК-Деветак-Невестино-Бяла Река-НХК</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>ДИРОСИ ООД</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>А1535ВВ</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
+      <c r="J48" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="J48" s="2" t="n">
+      <c r="K48" s="2" t="n">
         <v>10500</v>
       </c>
-      <c r="K48" s="2" t="n">
+      <c r="L48" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="L48" s="3" t="n">
+      <c r="M48" s="3" t="n">
         <v>22.85714285714286</v>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T48" s="4" t="n">
+      <c r="U48" s="4" t="n">
         <v>46085.7216528125</v>
       </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V48" s="4" t="n">
-        <v>46085.7247103125</v>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W48" s="4" t="n">
+        <v>46113.78193960648</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -4346,73 +4608,78 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>Варна-Терем-Енево-Варна</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>CB2201CC</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>P2849EE</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
+      <c r="J49" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="J49" s="2" t="n">
+      <c r="K49" s="2" t="n">
         <v>26000</v>
       </c>
-      <c r="K49" s="2" t="n">
+      <c r="L49" s="2" t="n">
         <v>133</v>
       </c>
-      <c r="L49" s="3" t="n">
+      <c r="M49" s="3" t="n">
         <v>5.115384615384615</v>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T49" s="4" t="n">
+      <c r="U49" s="4" t="n">
         <v>46085.72506998842</v>
       </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V49" s="4" t="n">
-        <v>46085.7265675463</v>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W49" s="4" t="n">
+        <v>46113.78193960648</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -4429,73 +4696,78 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>Варна-Добрич-Карапелит-Варна</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>CB2201CC</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>P2849EE</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
+      <c r="J50" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="J50" s="2" t="n">
+      <c r="K50" s="2" t="n">
         <v>26000</v>
       </c>
-      <c r="K50" s="2" t="n">
+      <c r="L50" s="2" t="n">
         <v>152</v>
       </c>
-      <c r="L50" s="3" t="n">
+      <c r="M50" s="3" t="n">
         <v>5.846153846153847</v>
       </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T50" s="4" t="n">
+      <c r="U50" s="4" t="n">
         <v>46085.72664005787</v>
       </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V50" s="4" t="n">
-        <v>46086.63388071759</v>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W50" s="4" t="n">
+        <v>46113.78193960648</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -4512,73 +4784,78 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t>Варна-Аспарухово-Тервел-Варна</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>"СИ-ТРАНС БЪЛГАРИЯ"  ЕООД</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Живко Демиров Вълчев</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>В9296ТМ</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>В6351ЕН</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
+      <c r="J51" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="J51" s="2" t="n">
+      <c r="K51" s="2" t="n">
         <v>30000</v>
       </c>
-      <c r="K51" s="2" t="n">
+      <c r="L51" s="2" t="n">
         <v>276</v>
       </c>
-      <c r="L51" s="3" t="n">
+      <c r="M51" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T51" s="4" t="n">
+      <c r="U51" s="4" t="n">
         <v>46085.72831567129</v>
       </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V51" s="4" t="n">
-        <v>46085.73147901621</v>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W51" s="4" t="n">
+        <v>46113.78193960648</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -4595,73 +4872,78 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>Варна-Аспарухово-Тервел-Брестак-Варна</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>CB2201CC</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>P2849EE</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
+      <c r="J52" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="J52" s="2" t="n">
+      <c r="K52" s="2" t="n">
         <v>34900</v>
       </c>
-      <c r="K52" s="2" t="n">
+      <c r="L52" s="2" t="n">
         <v>305</v>
       </c>
-      <c r="L52" s="3" t="n">
+      <c r="M52" s="3" t="n">
         <v>8.739255014326647</v>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T52" s="4" t="n">
+      <c r="U52" s="4" t="n">
         <v>46086.63388774305</v>
       </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V52" s="4" t="n">
-        <v>46086.63678805556</v>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W52" s="4" t="n">
+        <v>46113.78193960648</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>05</t>
         </is>
@@ -4678,73 +4960,78 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>Цар Калоян - Близнаци - Ушинци - Островче - Бяла</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Р7826КН</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>Р2530ЕЕ</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
+      <c r="J53" s="2" t="n">
         <v>222</v>
       </c>
-      <c r="J53" s="2" t="n">
+      <c r="K53" s="2" t="n">
         <v>7000</v>
       </c>
-      <c r="K53" s="2" t="n">
+      <c r="L53" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="L53" s="3" t="n">
+      <c r="M53" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T53" s="4" t="n">
+      <c r="U53" s="4" t="n">
         <v>46093.37681799768</v>
       </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V53" s="4" t="n">
-        <v>46093.37807652778</v>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W53" s="4" t="n">
+        <v>46113.78197206018</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -4761,68 +5048,73 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>Варна-Каварна-Варна</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>ТРАНС ОЙЛ ЕООД</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>B7902TM</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
+      <c r="J54" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="J54" s="2" t="n">
+      <c r="K54" s="2" t="n">
         <v>14000</v>
       </c>
-      <c r="K54" s="2" t="n">
+      <c r="L54" s="2" t="n">
         <v>152</v>
       </c>
-      <c r="L54" s="3" t="n">
+      <c r="M54" s="3" t="n">
         <v>10.85714285714286</v>
       </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T54" s="4" t="n">
+      <c r="U54" s="4" t="n">
         <v>46093.38065571759</v>
       </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V54" s="4" t="n">
-        <v>46093.4999272338</v>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W54" s="4" t="n">
+        <v>46113.78197206018</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -4839,73 +5131,78 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t>Варна-НХК-Добрич-Тервел-Варна</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>CB2201CC</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>P2849EE</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
+      <c r="J55" s="2" t="n">
         <v>490</v>
       </c>
-      <c r="J55" s="2" t="n">
+      <c r="K55" s="2" t="n">
         <v>32000</v>
       </c>
-      <c r="K55" s="2" t="n">
+      <c r="L55" s="2" t="n">
         <v>465</v>
       </c>
-      <c r="L55" s="3" t="n">
+      <c r="M55" s="3" t="n">
         <v>14.53125</v>
       </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T55" s="4" t="n">
+      <c r="U55" s="4" t="n">
         <v>46093.50014192129</v>
       </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V55" s="4" t="n">
-        <v>46093.50441935186</v>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W55" s="4" t="n">
+        <v>46113.78197206018</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -4922,68 +5219,73 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>НХК-Каблешково-НХК</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>ДИРОСИ ООД</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>А1535ВВ</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
+      <c r="J56" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="J56" s="2" t="n">
+      <c r="K56" s="2" t="n">
         <v>2000</v>
       </c>
-      <c r="K56" s="2" t="n">
+      <c r="L56" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="L56" s="3" t="n">
+      <c r="M56" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T56" s="4" t="n">
+      <c r="U56" s="4" t="n">
         <v>46093.50053460648</v>
       </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V56" s="4" t="n">
-        <v>46093.5017069213</v>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W56" s="4" t="n">
+        <v>46113.78197206018</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -5000,73 +5302,78 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t>Варна-НХК-Любен Каравелово-Смолница-Добрич-Варна</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>"СИ-ТРАНС БЪЛГАРИЯ"  ЕООД</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Живко Демиров Вълчев</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>В9296ТМ</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>В6351ЕН</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
+      <c r="J57" s="2" t="n">
         <v>440</v>
       </c>
-      <c r="J57" s="2" t="n">
+      <c r="K57" s="2" t="n">
         <v>30000</v>
       </c>
-      <c r="K57" s="2" t="n">
+      <c r="L57" s="2" t="n">
         <v>418</v>
       </c>
-      <c r="L57" s="3" t="n">
+      <c r="M57" s="3" t="n">
         <v>13.93333333333333</v>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T57" s="4" t="n">
+      <c r="U57" s="4" t="n">
         <v>46093.50452636574</v>
       </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V57" s="4" t="n">
-        <v>46093.50816883102</v>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W57" s="4" t="n">
+        <v>46113.78197206018</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -5083,73 +5390,78 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
           <t>Варна-Добрич-Каварна-Варна</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>CB2201CC</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>P2849EE</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
+      <c r="J58" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="J58" s="2" t="n">
+      <c r="K58" s="2" t="n">
         <v>30000</v>
       </c>
-      <c r="K58" s="2" t="n">
+      <c r="L58" s="2" t="n">
         <v>171</v>
       </c>
-      <c r="L58" s="3" t="n">
+      <c r="M58" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T58" s="4" t="n">
+      <c r="U58" s="4" t="n">
         <v>46093.51137797454</v>
       </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V58" s="4" t="n">
-        <v>46093.52349354167</v>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W58" s="4" t="n">
+        <v>46113.78197206018</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -5166,73 +5478,78 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
           <t>Варна-ЛУкойл Аспарухово-Тервел-Ген.Киселово-Добрич-Варна</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>CB2201CC</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>P2849EE</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
+      <c r="J59" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="J59" s="2" t="n">
+      <c r="K59" s="2" t="n">
         <v>32000</v>
       </c>
-      <c r="K59" s="2" t="n">
+      <c r="L59" s="2" t="n">
         <v>323</v>
       </c>
-      <c r="L59" s="3" t="n">
+      <c r="M59" s="3" t="n">
         <v>10.09375</v>
       </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T59" s="4" t="n">
+      <c r="U59" s="4" t="n">
         <v>46093.52361289352</v>
       </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V59" s="4" t="n">
-        <v>46093.52915773148</v>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W59" s="4" t="n">
+        <v>46113.78197206018</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -5249,73 +5566,78 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
           <t>Варна-Бяла-Кацелово-Ушинци-Енево-Невша-Варна</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>CB2201CC</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>P2849EE</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
+      <c r="J60" s="2" t="n">
         <v>440</v>
       </c>
-      <c r="J60" s="2" t="n">
+      <c r="K60" s="2" t="n">
         <v>33000</v>
       </c>
-      <c r="K60" s="2" t="n">
+      <c r="L60" s="2" t="n">
         <v>418</v>
       </c>
-      <c r="L60" s="3" t="n">
+      <c r="M60" s="3" t="n">
         <v>12.66666666666667</v>
       </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T60" s="4" t="n">
+      <c r="U60" s="4" t="n">
         <v>46093.52917561342</v>
       </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V60" s="4" t="n">
-        <v>46093.536381875</v>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W60" s="4" t="n">
+        <v>46113.78197206018</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -5332,73 +5654,78 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
           <t>Варна-Бяла-Тервел-Нова Камена-Жегларци-Карапелит-Караманите-Варна</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
+      <c r="J61" s="2" t="n">
         <v>530</v>
       </c>
-      <c r="J61" s="2" t="n">
+      <c r="K61" s="2" t="n">
         <v>30000</v>
       </c>
-      <c r="K61" s="2" t="n">
+      <c r="L61" s="2" t="n">
         <v>503</v>
       </c>
-      <c r="L61" s="3" t="n">
+      <c r="M61" s="3" t="n">
         <v>16.76666666666667</v>
       </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T61" s="4" t="n">
+      <c r="U61" s="4" t="n">
         <v>46093.53645888889</v>
       </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V61" s="4" t="n">
-        <v>46093.53874658565</v>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W61" s="4" t="n">
+        <v>46113.78197206018</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -5415,73 +5742,78 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t>Варна-НХК-Каварна-Добрич-Варна</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
+      <c r="J62" s="2" t="n">
         <v>460</v>
       </c>
-      <c r="J62" s="2" t="n">
+      <c r="K62" s="2" t="n">
         <v>30000</v>
       </c>
-      <c r="K62" s="2" t="n">
+      <c r="L62" s="2" t="n">
         <v>437</v>
       </c>
-      <c r="L62" s="3" t="n">
+      <c r="M62" s="3" t="n">
         <v>14.56666666666667</v>
       </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T62" s="4" t="n">
+      <c r="U62" s="4" t="n">
         <v>46093.53889314815</v>
       </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V62" s="4" t="n">
-        <v>46093.54026447917</v>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W62" s="4" t="n">
+        <v>46113.78197206018</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -5498,73 +5830,78 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
           <t>Варна-Пчелник-НХК-Пчелник-Девня-Тервел-Добрич-Варна</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>"СИ-ТРАНС БЪЛГАРИЯ"  ЕООД</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Живко Демиров Вълчев</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>В9296ТМ</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>В6351ЕН</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
+      <c r="J63" s="2" t="n">
         <v>510</v>
       </c>
-      <c r="J63" s="2" t="n">
+      <c r="K63" s="2" t="n">
         <v>38000</v>
       </c>
-      <c r="K63" s="2" t="n">
+      <c r="L63" s="2" t="n">
         <v>485</v>
       </c>
-      <c r="L63" s="3" t="n">
+      <c r="M63" s="3" t="n">
         <v>12.76315789473684</v>
       </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T63" s="4" t="n">
+      <c r="U63" s="4" t="n">
         <v>46094.63852730324</v>
       </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V63" s="4" t="n">
-        <v>46094.64747357639</v>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W63" s="4" t="n">
+        <v>46113.78197206018</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -5581,73 +5918,78 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t>Варна - Бяла - Тервел - Нова Камена - Кладенци - Жегларци - Повеляново -Варна</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
+      <c r="J64" s="2" t="n">
         <v>530</v>
       </c>
-      <c r="J64" s="2" t="n">
+      <c r="K64" s="2" t="n">
         <v>31500</v>
       </c>
-      <c r="K64" s="2" t="n">
+      <c r="L64" s="2" t="n">
         <v>504</v>
       </c>
-      <c r="L64" s="3" t="n">
+      <c r="M64" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T64" s="4" t="n">
+      <c r="U64" s="4" t="n">
         <v>46099.30808317129</v>
       </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V64" s="4" t="n">
-        <v>46099.31622158565</v>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W64" s="4" t="n">
+        <v>46113.78197206018</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -5664,73 +6006,78 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
           <t>Варна - Девня - Тервел - Добрич - Варна</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
+      <c r="J65" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="J65" s="2" t="n">
+      <c r="K65" s="2" t="n">
         <v>33000</v>
       </c>
-      <c r="K65" s="2" t="n">
+      <c r="L65" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="L65" s="3" t="n">
+      <c r="M65" s="3" t="n">
         <v>5.757575757575758</v>
       </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T65" s="4" t="n">
+      <c r="U65" s="4" t="n">
         <v>46099.31630357639</v>
       </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V65" s="4" t="n">
-        <v>46099.31850265047</v>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W65" s="4" t="n">
+        <v>46113.78197206018</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -5747,73 +6094,78 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
           <t>Варна - Провадия - Енево - Ведрина - Добрич - Каварна - Варна</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
+      <c r="J66" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="J66" s="2" t="n">
+      <c r="K66" s="2" t="n">
         <v>31600</v>
       </c>
-      <c r="K66" s="2" t="n">
+      <c r="L66" s="2" t="n">
         <v>276</v>
       </c>
-      <c r="L66" s="3" t="n">
+      <c r="M66" s="3" t="n">
         <v>8.734177215189874</v>
       </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T66" s="4" t="n">
+      <c r="U66" s="4" t="n">
         <v>46099.3186015625</v>
       </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V66" s="4" t="n">
-        <v>46099.32178516204</v>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W66" s="4" t="n">
+        <v>46113.78197206018</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -5830,73 +6182,78 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
           <t>Варна - Плевен - Варна - Карапелит - Добрич - Каварна - Варна</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
+      <c r="J67" s="2" t="n">
         <v>870</v>
       </c>
-      <c r="J67" s="2" t="n">
+      <c r="K67" s="2" t="n">
         <v>30500</v>
       </c>
-      <c r="K67" s="2" t="n">
+      <c r="L67" s="2" t="n">
         <v>830</v>
       </c>
-      <c r="L67" s="3" t="n">
+      <c r="M67" s="3" t="n">
         <v>27.21311475409836</v>
       </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T67" s="4" t="n">
+      <c r="U67" s="4" t="n">
         <v>46099.32193038194</v>
       </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V67" s="4" t="n">
-        <v>46099.32392136574</v>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W67" s="4" t="n">
+        <v>46113.78197206018</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -5913,73 +6270,78 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
           <t>Бяла- Долни Дъбник - Луковит - Орешец - Враца</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>CB2201CC</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>P2849EE</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
+      <c r="J68" s="2" t="n">
         <v>420</v>
       </c>
-      <c r="J68" s="2" t="n">
+      <c r="K68" s="2" t="n">
         <v>32000</v>
       </c>
-      <c r="K68" s="2" t="n">
+      <c r="L68" s="2" t="n">
         <v>399</v>
       </c>
-      <c r="L68" s="3" t="n">
+      <c r="M68" s="3" t="n">
         <v>12.46875</v>
       </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T68" s="4" t="n">
+      <c r="U68" s="4" t="n">
         <v>46099.32401704861</v>
       </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V68" s="4" t="n">
-        <v>46099.32668708333</v>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W68" s="4" t="n">
+        <v>46113.78197206018</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -5996,73 +6358,78 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
           <t>Русе-Тервел-Добрич-Каварна-Стожер-Повеляново-Енево-Русе</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>Р7826КН</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>Р2530ЕЕ</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
+      <c r="J69" s="2" t="n">
         <v>520</v>
       </c>
-      <c r="J69" s="2" t="n">
+      <c r="K69" s="2" t="n">
         <v>29500</v>
       </c>
-      <c r="K69" s="2" t="n">
+      <c r="L69" s="2" t="n">
         <v>494</v>
       </c>
-      <c r="L69" s="3" t="n">
+      <c r="M69" s="3" t="n">
         <v>16.7457627118644</v>
       </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T69" s="4" t="n">
+      <c r="U69" s="4" t="n">
         <v>46099.32677207176</v>
       </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V69" s="4" t="n">
-        <v>46100.53311954861</v>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W69" s="4" t="n">
+        <v>46113.78201332176</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -6079,73 +6446,81 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
           <t>Бяла-Тервел-Добрич-Ген.Колево-Русе</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>Р7826КН</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>Р2530ЕЕ</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
+      <c r="J70" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="J70" s="2" t="n">
+      <c r="K70" s="2" t="n">
         <v>32000</v>
       </c>
-      <c r="K70" s="2" t="n">
+      <c r="L70" s="2" t="n">
         <v>475</v>
       </c>
-      <c r="L70" s="3" t="n">
+      <c r="M70" s="3" t="n">
         <v>14.84375</v>
       </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="Q70" s="3" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="T70" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T70" s="4" t="n">
+      <c r="U70" s="4" t="n">
         <v>46099.32958340278</v>
       </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V70" s="4" t="n">
-        <v>46100.53345317129</v>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W70" s="4" t="n">
+        <v>46113.78201332176</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -6162,78 +6537,83 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
           <t>Варна-Нефтохим-Пчелник-Девня-Добрич-Варна</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>"СИ-ТРАНС БЪЛГАРИЯ"  ЕООД</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Живко Демиров Вълчев</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>В9296ТМ</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>В6351ЕН</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
+      <c r="J71" s="2" t="n">
         <v>430</v>
       </c>
-      <c r="J71" s="2" t="n">
+      <c r="K71" s="2" t="n">
         <v>31500</v>
       </c>
-      <c r="K71" s="2" t="n">
+      <c r="L71" s="2" t="n">
         <v>430</v>
       </c>
-      <c r="L71" s="3" t="n">
+      <c r="M71" s="3" t="n">
         <v>13.65079365079365</v>
       </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
       <c r="O71" t="inlineStr">
         <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
           <t>Повишен транспорт - по 1евро на км без ДДС</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T71" s="4" t="n">
+      <c r="U71" s="4" t="n">
         <v>46100.53290248843</v>
       </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V71" s="4" t="n">
-        <v>46100.53596527778</v>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W71" s="4" t="n">
+        <v>46113.78201332176</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -6250,73 +6630,78 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
           <t>Варна-Повеляново-Блъсково-Неново-Добрич-Варна</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I72" s="2" t="n">
+      <c r="J72" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="J72" s="2" t="n">
+      <c r="K72" s="2" t="n">
         <v>30000</v>
       </c>
-      <c r="K72" s="2" t="n">
+      <c r="L72" s="2" t="n">
         <v>228</v>
       </c>
-      <c r="L72" s="3" t="n">
+      <c r="M72" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T72" s="4" t="n">
+      <c r="U72" s="4" t="n">
         <v>46104.46047940972</v>
       </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V72" s="4" t="n">
-        <v>46104.47593141204</v>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W72" s="4" t="n">
+        <v>46113.78201332176</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -6333,73 +6718,78 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
           <t>Бяла-Тервел-Безмер-Северняк-Крапец-Бяла</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>CB2201CC</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>P2849EE</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
+      <c r="J73" s="2" t="n">
         <v>670</v>
       </c>
-      <c r="J73" s="2" t="n">
+      <c r="K73" s="2" t="n">
         <v>32000</v>
       </c>
-      <c r="K73" s="2" t="n">
+      <c r="L73" s="2" t="n">
         <v>670</v>
       </c>
-      <c r="L73" s="3" t="n">
+      <c r="M73" s="3" t="n">
         <v>20.9375</v>
       </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T73" s="4" t="n">
+      <c r="U73" s="4" t="n">
         <v>46108.35512471065</v>
       </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V73" s="4" t="n">
-        <v>46108.35684398148</v>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W73" s="4" t="n">
+        <v>46113.78201332176</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -6416,73 +6806,78 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
           <t>Варна-Девня-Бяла-Девня-Доброплодно-Вълчи дол-Опанец-Добрич-Варна</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I74" s="2" t="n">
+      <c r="J74" s="2" t="n">
         <v>530</v>
       </c>
-      <c r="J74" s="2" t="n">
+      <c r="K74" s="2" t="n">
         <v>37300</v>
       </c>
-      <c r="K74" s="2" t="n">
+      <c r="L74" s="2" t="n">
         <v>530</v>
       </c>
-      <c r="L74" s="3" t="n">
+      <c r="M74" s="3" t="n">
         <v>14.20911528150134</v>
       </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T74" s="4" t="n">
+      <c r="U74" s="4" t="n">
         <v>46108.35836797454</v>
       </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V74" s="4" t="n">
-        <v>46108.35978013889</v>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W74" s="4" t="n">
+        <v>46113.78201332176</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -6499,73 +6894,78 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
           <t>Варна-Русе-Тервел-Добрич-Каварна-Варна</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
+      <c r="J75" s="2" t="n">
         <v>530</v>
       </c>
-      <c r="J75" s="2" t="n">
+      <c r="K75" s="2" t="n">
         <v>30000</v>
       </c>
-      <c r="K75" s="2" t="n">
+      <c r="L75" s="2" t="n">
         <v>530</v>
       </c>
-      <c r="L75" s="3" t="n">
+      <c r="M75" s="3" t="n">
         <v>17.66666666666667</v>
       </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr">
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T75" s="4" t="n">
+      <c r="U75" s="4" t="n">
         <v>46108.36046548611</v>
       </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V75" s="4" t="n">
-        <v>46108.36212280093</v>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W75" s="4" t="n">
+        <v>46113.78201332176</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -6582,73 +6982,78 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
           <t>Варна-Бяла-Енево-Добрич-Варна</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I76" s="2" t="n">
+      <c r="J76" s="2" t="n">
         <v>530</v>
       </c>
-      <c r="J76" s="2" t="n">
+      <c r="K76" s="2" t="n">
         <v>30000</v>
       </c>
-      <c r="K76" s="2" t="n">
+      <c r="L76" s="2" t="n">
         <v>530</v>
       </c>
-      <c r="L76" s="3" t="n">
+      <c r="M76" s="3" t="n">
         <v>17.66666666666667</v>
       </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr">
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T76" s="4" t="n">
+      <c r="U76" s="4" t="n">
         <v>46108.36223175926</v>
       </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V76" s="4" t="n">
-        <v>46108.36351108796</v>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W76" s="4" t="n">
+        <v>46113.78201332176</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -6665,73 +7070,81 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
           <t>Бяла-Тервел-Карапелит-Бяла</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>Р7826КН</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>Р2530ЕЕ</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
+      <c r="J77" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="J77" s="2" t="n">
+      <c r="K77" s="2" t="n">
         <v>32000</v>
       </c>
-      <c r="K77" s="2" t="n">
+      <c r="L77" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="L77" s="3" t="n">
+      <c r="M77" s="3" t="n">
         <v>14.0625</v>
       </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="Q77" s="3" t="n">
+        <v>47.81</v>
+      </c>
+      <c r="T77" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T77" s="4" t="n">
+      <c r="U77" s="4" t="n">
         <v>46108.36367075232</v>
       </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V77" s="4" t="n">
-        <v>46108.40357136574</v>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W77" s="4" t="n">
+        <v>46113.78201332176</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -6748,73 +7161,78 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
           <t>Варна-Повеляново-Варна</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I78" s="2" t="n">
+      <c r="J78" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="J78" s="2" t="n">
+      <c r="K78" s="2" t="n">
         <v>11000</v>
       </c>
-      <c r="K78" s="2" t="n">
+      <c r="L78" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="L78" s="3" t="n">
+      <c r="M78" s="3" t="n">
         <v>5.454545454545455</v>
       </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr">
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T78" s="4" t="n">
+      <c r="U78" s="4" t="n">
         <v>46108.40366939815</v>
       </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V78" s="4" t="n">
-        <v>46108.40500577546</v>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W78" s="4" t="n">
+        <v>46113.78201332176</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -6831,73 +7249,78 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
           <t>Бяла-Вълчи дол-Ген. Киселово-Стожер-Добрич-Тервел-Войново-Бяла</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>Р7826КН</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>Р2530ЕЕ</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
+      <c r="J79" s="2" t="n">
         <v>530</v>
       </c>
-      <c r="J79" s="2" t="n">
+      <c r="K79" s="2" t="n">
         <v>32000</v>
       </c>
-      <c r="K79" s="2" t="n">
+      <c r="L79" s="2" t="n">
         <v>530</v>
       </c>
-      <c r="L79" s="3" t="n">
+      <c r="M79" s="3" t="n">
         <v>16.5625</v>
       </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S79" t="inlineStr">
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T79" s="4" t="n">
+      <c r="U79" s="4" t="n">
         <v>46111.39227858796</v>
       </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V79" s="4" t="n">
-        <v>46111.39422512732</v>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W79" s="4" t="n">
+        <v>46113.78201332176</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -6914,73 +7337,78 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
           <t>Варна-Бяла-Русе-Добрич-Каварна-Варна</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I80" s="2" t="n">
+      <c r="J80" s="2" t="n">
         <v>580</v>
       </c>
-      <c r="J80" s="2" t="n">
+      <c r="K80" s="2" t="n">
         <v>30000</v>
       </c>
-      <c r="K80" s="2" t="n">
+      <c r="L80" s="2" t="n">
         <v>580</v>
       </c>
-      <c r="L80" s="3" t="n">
+      <c r="M80" s="3" t="n">
         <v>19.33333333333334</v>
       </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S80" t="inlineStr">
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T80" s="4" t="n">
+      <c r="U80" s="4" t="n">
         <v>46111.39427806713</v>
       </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V80" s="4" t="n">
-        <v>46111.3953196875</v>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W80" s="4" t="n">
+        <v>46113.78201332176</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -6997,73 +7425,78 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
           <t>Варна-Девня-Добрич-Варна</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>Р9581МА</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>Р4961ЕЕ</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
+      <c r="J81" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="J81" s="2" t="n">
+      <c r="K81" s="2" t="n">
         <v>34000</v>
       </c>
-      <c r="K81" s="2" t="n">
+      <c r="L81" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="L81" s="3" t="n">
+      <c r="M81" s="3" t="n">
         <v>4.411764705882353</v>
       </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S81" t="inlineStr">
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T81" s="4" t="n">
+      <c r="U81" s="4" t="n">
         <v>46111.39548138889</v>
       </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Vesela Nikolova</t>
-        </is>
-      </c>
-      <c r="V81" s="4" t="n">
-        <v>46111.39747710648</v>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W81" s="4" t="n">
+        <v>46113.78201332176</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -7080,70 +7513,1201 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
           <t>Варна-Сенокос-Варна</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>ТРАНС ОЙЛ ЕООД</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>B7902TM</t>
         </is>
       </c>
-      <c r="I82" s="2" t="n">
+      <c r="J82" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="J82" s="2" t="n">
+      <c r="K82" s="2" t="n">
         <v>18000</v>
       </c>
-      <c r="K82" s="2" t="n">
+      <c r="L82" s="2" t="n">
         <v>152</v>
       </c>
-      <c r="L82" s="3" t="n">
+      <c r="M82" s="3" t="n">
         <v>8.444444444444443</v>
       </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>НЕПЛАТЕНА</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr">
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="T82" s="4" t="n">
+      <c r="U82" s="4" t="n">
         <v>46112.6286593287</v>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W82" s="4" t="n">
+        <v>46113.78382233797</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="19.2" customHeight="1">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20260401-0001</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="n">
+        <v>46058</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Русе-Червена вода-Русе</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="M83" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Офис София</t>
+        </is>
+      </c>
+      <c r="Q83" s="3" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="T83" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
         </is>
       </c>
-      <c r="V82" s="4" t="n">
-        <v>46112.65841324074</v>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
+      <c r="U83" s="4" t="n">
+        <v>46113.42261793982</v>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W83" s="4" t="n">
+        <v>46113.78213268518</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
         <is>
           <t>04</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="19.2" customHeight="1">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20260401-0002</t>
+        </is>
+      </c>
+      <c r="B84" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Русе-Червена вода-Русе
+​</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M84" s="3" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Офис София</t>
+        </is>
+      </c>
+      <c r="Q84" s="3" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U84" s="4" t="n">
+        <v>46113.42439645834</v>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W84" s="4" t="n">
+        <v>46113.78213268518</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="19.2" customHeight="1">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>20260401-0003</t>
+        </is>
+      </c>
+      <c r="B85" s="1" t="n">
+        <v>46071</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Русе-Бяла-Оряхово-Русе</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>435</v>
+      </c>
+      <c r="M85" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Офис София</t>
+        </is>
+      </c>
+      <c r="Q85" s="3" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U85" s="4" t="n">
+        <v>46113.42645094907</v>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W85" s="4" t="n">
+        <v>46113.78213268518</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="19.2" customHeight="1">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>20260401-0004</t>
+        </is>
+      </c>
+      <c r="B86" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Русе-Бяла-Оряхово-Кула-Русе</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>760</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>810</v>
+      </c>
+      <c r="M86" s="3" t="n">
+        <v>26.12903225806452</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Офис София</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U86" s="4" t="n">
+        <v>46113.43727493055</v>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W86" s="4" t="n">
+        <v>46113.78217078704</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="19.2" customHeight="1">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>20260401-0005</t>
+        </is>
+      </c>
+      <c r="B87" s="1" t="n">
+        <v>46058</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Русе-Бяла-Никопол-Русе</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="M87" s="3" t="n">
+        <v>8.387096774193548</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Офис София</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U87" s="4" t="n">
+        <v>46113.43905060185</v>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W87" s="4" t="n">
+        <v>46113.78217078704</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="19.2" customHeight="1">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>20260401-0006</t>
+        </is>
+      </c>
+      <c r="B88" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Русе-Павликени-Ловеч-Плевен</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="M88" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Офис София</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U88" s="4" t="n">
+        <v>46113.4439542824</v>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W88" s="4" t="n">
+        <v>46113.78217078704</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="19.2" customHeight="1">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>20260401-0007</t>
+        </is>
+      </c>
+      <c r="B89" s="1" t="n">
+        <v>46065</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Плевен-София-Бяла</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>423</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="M89" s="3" t="n">
+        <v>21.33333333333333</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Офис София</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U89" s="4" t="n">
+        <v>46113.4468446875</v>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W89" s="4" t="n">
+        <v>46113.78217078704</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="19.2" customHeight="1">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>20260401-0008</t>
+        </is>
+      </c>
+      <c r="B90" s="1" t="n">
+        <v>46066</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Бяла-Русе</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="M90" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Офис София</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U90" s="4" t="n">
+        <v>46113.44918413195</v>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W90" s="4" t="n">
+        <v>46113.78217078704</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="19.2" customHeight="1">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>20260401-0009</t>
+        </is>
+      </c>
+      <c r="B91" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Русе-Павликени-Ловеч-д.Луковит-Русе</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>29000</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>460</v>
+      </c>
+      <c r="M91" s="3" t="n">
+        <v>15.86206896551724</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Офис София</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U91" s="4" t="n">
+        <v>46113.45028952546</v>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W91" s="4" t="n">
+        <v>46113.78217078704</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="19.2" customHeight="1">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>20260401-0010</t>
+        </is>
+      </c>
+      <c r="B92" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Русе-Плевен-София</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="M92" s="3" t="n">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Офис София</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U92" s="4" t="n">
+        <v>46113.4637524537</v>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W92" s="4" t="n">
+        <v>46113.78217078704</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="19.2" customHeight="1">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>20260401-0011</t>
+        </is>
+      </c>
+      <c r="B93" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>София-Радомир-Плевен</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>270</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="M93" s="3" t="n">
+        <v>5.454545454545455</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Офис София</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U93" s="4" t="n">
+        <v>46113.46653799769</v>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W93" s="4" t="n">
+        <v>46113.78217078704</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="19.2" customHeight="1">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>20260401-0012</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="n">
+        <v>46078</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Плевен-Хасково-Любимец-Поморие-Ахелой-Каблешково-Варна-Русе</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>850</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M94" s="3" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Офис София</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U94" s="4" t="n">
+        <v>46113.46807900463</v>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W94" s="4" t="n">
+        <v>46113.78217078704</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>01</t>
         </is>
       </c>
     </row>

--- a/transport/transport_data.xlsx
+++ b/transport/transport_data.xlsx
@@ -7596,7 +7596,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ОФИС ВАРНА</t>
+          <t>ОФИС СОФИЯ</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7659,11 +7659,11 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>Plamen Svetoslavov</t>
+          <t>Vesela Nikolova</t>
         </is>
       </c>
       <c r="W83" s="4" t="n">
-        <v>46113.78213268518</v>
+        <v>46113.82213099537</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ОФИС ВАРНА</t>
+          <t>ОФИС СОФИЯ</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7756,11 +7756,11 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>Plamen Svetoslavov</t>
+          <t>Vesela Nikolova</t>
         </is>
       </c>
       <c r="W84" s="4" t="n">
-        <v>46113.78213268518</v>
+        <v>46113.82214940972</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ОФИС ВАРНА</t>
+          <t>ОФИС СОФИЯ</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7852,11 +7852,11 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>Plamen Svetoslavov</t>
+          <t>Vesela Nikolova</t>
         </is>
       </c>
       <c r="W85" s="4" t="n">
-        <v>46113.78213268518</v>
+        <v>46113.82218974537</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ОФИС ВАРНА</t>
+          <t>ОФИС СОФИЯ</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7945,11 +7945,11 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>Plamen Svetoslavov</t>
+          <t>Vesela Nikolova</t>
         </is>
       </c>
       <c r="W86" s="4" t="n">
-        <v>46113.78217078704</v>
+        <v>46113.82221420139</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ОФИС ВАРНА</t>
+          <t>ОФИС СОФИЯ</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -8038,11 +8038,11 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>Plamen Svetoslavov</t>
+          <t>Vesela Nikolova</t>
         </is>
       </c>
       <c r="W87" s="4" t="n">
-        <v>46113.78217078704</v>
+        <v>46113.82223347222</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ОФИС ВАРНА</t>
+          <t>ОФИС СОФИЯ</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -8131,11 +8131,11 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>Plamen Svetoslavov</t>
+          <t>Vesela Nikolova</t>
         </is>
       </c>
       <c r="W88" s="4" t="n">
-        <v>46113.78217078704</v>
+        <v>46113.82226113426</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ОФИС ВАРНА</t>
+          <t>ОФИС СОФИЯ</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -8224,11 +8224,11 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>Plamen Svetoslavov</t>
+          <t>Vesela Nikolova</t>
         </is>
       </c>
       <c r="W89" s="4" t="n">
-        <v>46113.78217078704</v>
+        <v>46113.82230854167</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ОФИС ВАРНА</t>
+          <t>ОФИС СОФИЯ</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8317,11 +8317,11 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>Plamen Svetoslavov</t>
+          <t>Vesela Nikolova</t>
         </is>
       </c>
       <c r="W90" s="4" t="n">
-        <v>46113.78217078704</v>
+        <v>46113.82234298611</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ОФИС ВАРНА</t>
+          <t>ОФИС СОФИЯ</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8410,11 +8410,11 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>Plamen Svetoslavov</t>
+          <t>Vesela Nikolova</t>
         </is>
       </c>
       <c r="W91" s="4" t="n">
-        <v>46113.78217078704</v>
+        <v>46113.82236216435</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ОФИС ВАРНА</t>
+          <t>ОФИС СОФИЯ</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8503,11 +8503,11 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>Plamen Svetoslavov</t>
+          <t>Vesela Nikolova</t>
         </is>
       </c>
       <c r="W92" s="4" t="n">
-        <v>46113.78217078704</v>
+        <v>46113.82241850694</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ОФИС ВАРНА</t>
+          <t>ОФИС СОФИЯ</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -8596,11 +8596,11 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>Plamen Svetoslavov</t>
+          <t>Vesela Nikolova</t>
         </is>
       </c>
       <c r="W93" s="4" t="n">
-        <v>46113.78217078704</v>
+        <v>46113.82243373842</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ОФИС ВАРНА</t>
+          <t>ОФИС СОФИЯ</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -8689,11 +8689,11 @@
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>Plamen Svetoslavov</t>
+          <t>Vesela Nikolova</t>
         </is>
       </c>
       <c r="W94" s="4" t="n">
-        <v>46113.78217078704</v>
+        <v>46113.82246005787</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>

--- a/transport/transport_data.xlsx
+++ b/transport/transport_data.xlsx
@@ -407,7 +407,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>МАРШРУТ_СНИМКА</t>
+          <t>БРОЙ_ОБЕКТИ</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -2098,11 +2098,6 @@
           <t>Варна-Суворово-Варна</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>{'name': 'viber_image_2026-02-06_17-32-49-760.jpg', 'size': 185211, 'type': 'file', 'upload_time': '2026-02-06T15:33:22.822+00:00', 'url': 'https://cloud.seatable.io/workspace/73766/asset/9ebe8e8a-2c5f-44c3-afdf-b98ab8a88929/external-apps/files/2026-02/viber_image_2026-02-06_17-32-49-760.jpg'}</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>"СИ-ТРАНС БЪЛГАРИЯ"  ЕООД</t>
@@ -5865,10 +5860,10 @@
         <v>38000</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>485</v>
+        <v>535</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>12.76315789473684</v>
+        <v>14.07894736842105</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -5885,11 +5880,11 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>Plamen Svetoslavov</t>
+          <t>Vesela Nikolova</t>
         </is>
       </c>
       <c r="W63" s="4" t="n">
-        <v>46113.78197206018</v>
+        <v>46126.42932174769</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6572,10 +6567,10 @@
         <v>31500</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>13.65079365079365</v>
+        <v>14.34920634920635</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6597,11 +6592,11 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>Plamen Svetoslavov</t>
+          <t>Vesela Nikolova</t>
         </is>
       </c>
       <c r="W71" s="4" t="n">
-        <v>46113.78201332176</v>
+        <v>46126.4276888426</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -8708,6 +8703,3060 @@
       <c r="Z94" t="inlineStr">
         <is>
           <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="19.2" customHeight="1">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>20260402-0001</t>
+        </is>
+      </c>
+      <c r="B95" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Варна-Каварна-Добрич-Енево-Провадия-Дългопол-Варна</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>408</v>
+      </c>
+      <c r="M95" s="3" t="n">
+        <v>12.36363636363636</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U95" s="4" t="n">
+        <v>46114.4417537037</v>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W95" s="4" t="n">
+        <v>46119.59090974537</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="19.2" customHeight="1">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>20260402-0002</t>
+        </is>
+      </c>
+      <c r="B96" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Варна-Бяла-Енево-Тервел-Карапелит-Добрич-Ботево-Варна</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>540</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="M96" s="3" t="n">
+        <v>19.93846153846154</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U96" s="4" t="n">
+        <v>46114.44175608797</v>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W96" s="4" t="n">
+        <v>46119.59081111111</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="19.2" customHeight="1">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>20260402-0003</t>
+        </is>
+      </c>
+      <c r="B97" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ОФИС СОФИЯ</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Русе-Бяла-Плевен-Айтос-Поморие-Русе</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>870</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>39900</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>1044</v>
+      </c>
+      <c r="M97" s="3" t="n">
+        <v>26.16541353383458</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U97" s="4" t="n">
+        <v>46114.45008017361</v>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W97" s="4" t="n">
+        <v>46119.59068777777</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="19.2" customHeight="1">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>20260402-0004</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Русе-Бяла-Орешец-Берковица-Враца</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>27000</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>564</v>
+      </c>
+      <c r="M98" s="3" t="n">
+        <v>20.88888888888889</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U98" s="4" t="n">
+        <v>46114.45399453703</v>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W98" s="4" t="n">
+        <v>46119.59059599537</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="19.2" customHeight="1">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>20260407-0001</t>
+        </is>
+      </c>
+      <c r="B99" s="1" t="n">
+        <v>46118</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="M99" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U99" s="4" t="n">
+        <v>46119.58348922454</v>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W99" s="4" t="n">
+        <v>46119.59397283565</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="19.2" customHeight="1">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>20260407-0002</t>
+        </is>
+      </c>
+      <c r="B100" s="1" t="n">
+        <v>46115</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>варна-Чефо-Добрич-варна</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="M100" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U100" s="4" t="n">
+        <v>46119.58349258102</v>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W100" s="4" t="n">
+        <v>46119.59046303241</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="19.2" customHeight="1">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>20260407-0003</t>
+        </is>
+      </c>
+      <c r="B101" s="1" t="n">
+        <v>46118</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Варна-Повеляново-Калиманци-Любен Каравелово - Вълчи дол - Сенокос- Каварна-Варна</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>41000</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="M101" s="3" t="n">
+        <v>8.780487804878049</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U101" s="4" t="n">
+        <v>46119.59406583333</v>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W101" s="4" t="n">
+        <v>46119.59755049769</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="19.2" customHeight="1">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>20260407-0004</t>
+        </is>
+      </c>
+      <c r="B102" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Русе-Тервел-Добрич-Стожер-Ушинци-Русе</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>34500</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>528</v>
+      </c>
+      <c r="M102" s="3" t="n">
+        <v>15.30434782608696</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U102" s="4" t="n">
+        <v>46119.59664443287</v>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W102" s="4" t="n">
+        <v>46119.59941574074</v>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="19.2" customHeight="1">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>20260407-0005</t>
+        </is>
+      </c>
+      <c r="B103" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Варна-Девня-Добрич-Ген Колево-Ген. Тошево - Каварна - Варна</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>276</v>
+      </c>
+      <c r="M103" s="3" t="n">
+        <v>8.625</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U103" s="4" t="n">
+        <v>46119.59958134259</v>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W103" s="4" t="n">
+        <v>46119.60275851852</v>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="19.2" customHeight="1">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>20260407-0006</t>
+        </is>
+      </c>
+      <c r="B104" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-Карапелит-Жегларци-Варна</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>30800</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="M104" s="3" t="n">
+        <v>10.12987012987013</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U104" s="4" t="n">
+        <v>46119.60286013889</v>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W104" s="4" t="n">
+        <v>46119.60561114583</v>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="19.2" customHeight="1">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>20260407-0007</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Варна-Бяла-Тервел-Нова Камена-Варна</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>510</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>612</v>
+      </c>
+      <c r="M105" s="3" t="n">
+        <v>19.125</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U105" s="4" t="n">
+        <v>46119.60641738426</v>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W105" s="4" t="n">
+        <v>46121.37460918981</v>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="19.2" customHeight="1">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>20260407-0008</t>
+        </is>
+      </c>
+      <c r="B106" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Варна-Бяла-Добрич-Каварна-Варна</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>660</v>
+      </c>
+      <c r="M106" s="3" t="n">
+        <v>20.625</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U106" s="4" t="n">
+        <v>46119.60840902778</v>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W106" s="4" t="n">
+        <v>46121.37533226852</v>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="19.2" customHeight="1">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>20260414-0001</t>
+        </is>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Русе-Бяла-Търговище-Шумен-Снежина-Русе</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>456</v>
+      </c>
+      <c r="M107" s="3" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U107" s="4" t="n">
+        <v>46126.38869865741</v>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W107" s="4" t="n">
+        <v>46126.39018428241</v>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="19.2" customHeight="1">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>20260414-0002</t>
+        </is>
+      </c>
+      <c r="B108" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Варна-Русе-Бяла-Девня-Добрич-Каварна-Варна</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>720</v>
+      </c>
+      <c r="M108" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U108" s="4" t="n">
+        <v>46126.3906471875</v>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W108" s="4" t="n">
+        <v>46126.39402790509</v>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="19.2" customHeight="1">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>20260414-0003</t>
+        </is>
+      </c>
+      <c r="B109" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Русе-Бяла-Тервел-Добрич-Русе</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="M109" s="3" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U109" s="4" t="n">
+        <v>46126.39436719907</v>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W109" s="4" t="n">
+        <v>46126.39566355324</v>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="19.2" customHeight="1">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>20260424-0001</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Варна-Бяла-Блъсково-Повеляново-Варна-Стожер-Добрич-Ген.Киселово-Брестак-Есеница-Карапелит-Окорш-Бяла</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>960</v>
+      </c>
+      <c r="M110" s="3" t="n">
+        <v>30.96774193548387</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U110" s="4" t="n">
+        <v>46136.67863891204</v>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W110" s="4" t="n">
+        <v>46136.68043775463</v>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="19.2" customHeight="1">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>20260424-0002</t>
+        </is>
+      </c>
+      <c r="B111" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Варна-Бяла-Добрич-Каварна-варна</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>660</v>
+      </c>
+      <c r="M111" s="3" t="n">
+        <v>20.625</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U111" s="4" t="n">
+        <v>46136.68062988426</v>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W111" s="4" t="n">
+        <v>46136.69066723379</v>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="19.2" customHeight="1">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>20260424-0003</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Русе-Бяла-Тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="M112" s="3" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U112" s="4" t="n">
+        <v>46136.69078819444</v>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W112" s="4" t="n">
+        <v>46136.69432903935</v>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="19.2" customHeight="1">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>20260424-0004</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Варна-Русе-Бяла-Каварна-Близнаци-Повеляново-Варна</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>580</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>696</v>
+      </c>
+      <c r="M113" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U113" s="4" t="n">
+        <v>46136.69437859954</v>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W113" s="4" t="n">
+        <v>46136.69595549769</v>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="19.2" customHeight="1">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>20260424-0005</t>
+        </is>
+      </c>
+      <c r="B114" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="M114" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U114" s="4" t="n">
+        <v>46136.69599675926</v>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W114" s="4" t="n">
+        <v>46136.69708907408</v>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="19.2" customHeight="1">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>20260424-0006</t>
+        </is>
+      </c>
+      <c r="B115" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Бяла-Ловеч-Павликени-Бяла</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="M115" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U115" s="4" t="n">
+        <v>46136.69714005787</v>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W115" s="4" t="n">
+        <v>46136.70557487269</v>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="19.2" customHeight="1">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>20260424-0007</t>
+        </is>
+      </c>
+      <c r="B116" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Варна-Бяла-Тервел-Добрич-Малина-Каварна-Варна</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>570</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>690</v>
+      </c>
+      <c r="M116" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U116" s="4" t="n">
+        <v>46136.70620979166</v>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W116" s="4" t="n">
+        <v>46136.70717837963</v>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="19.2" customHeight="1">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>20260424-0008</t>
+        </is>
+      </c>
+      <c r="B117" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-Повеляново-Варна</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="M117" s="3" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U117" s="4" t="n">
+        <v>46136.7072147338</v>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W117" s="4" t="n">
+        <v>46136.7084734375</v>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="19.2" customHeight="1">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>20260424-0009</t>
+        </is>
+      </c>
+      <c r="B118" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Варна-Сл.Бряг-Несебър-НХК-Риш-Нова Бяла Река-Провадия-Енево-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>510</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>42500</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>510</v>
+      </c>
+      <c r="M118" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U118" s="4" t="n">
+        <v>46136.70855460648</v>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W118" s="4" t="n">
+        <v>46136.7159302662</v>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="19.2" customHeight="1">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>20260424-0010</t>
+        </is>
+      </c>
+      <c r="B119" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Русе-тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="M119" s="3" t="n">
+        <v>10.3125</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U119" s="4" t="n">
+        <v>46136.71483799769</v>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W119" s="4" t="n">
+        <v>46136.71601056713</v>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="19.2" customHeight="1">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>20260424-0011</t>
+        </is>
+      </c>
+      <c r="B120" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Русе-Бяла-Лом-Орешец-Русе</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>840</v>
+      </c>
+      <c r="M120" s="3" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U120" s="4" t="n">
+        <v>46136.71606890046</v>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W120" s="4" t="n">
+        <v>46136.71730175926</v>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="19.2" customHeight="1">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>20260428-0001</t>
+        </is>
+      </c>
+      <c r="B121" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>НХК-Каблешково-НХК</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>А1535ВВ</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="M121" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U121" s="4" t="n">
+        <v>46140.64835413195</v>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W121" s="4" t="n">
+        <v>46140.65173761574</v>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="19.2" customHeight="1">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>20260428-0002</t>
+        </is>
+      </c>
+      <c r="B122" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ВАРНА-девня-Варна</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="M122" s="3" t="n">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U122" s="4" t="n">
+        <v>46140.65242412037</v>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W122" s="4" t="n">
+        <v>46140.66494774305</v>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="19.2" customHeight="1">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>20260428-0003</t>
+        </is>
+      </c>
+      <c r="B123" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>26000</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="M123" s="3" t="n">
+        <v>5.538461538461538</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U123" s="4" t="n">
+        <v>46140.66499206018</v>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W123" s="4" t="n">
+        <v>46140.66614908565</v>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="19.2" customHeight="1">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>20260428-0004</t>
+        </is>
+      </c>
+      <c r="B124" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Варна-Долни Чифлик- Невестино- Деветак - НХК</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>14500</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="M124" s="3" t="n">
+        <v>24.82758620689655</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U124" s="4" t="n">
+        <v>46140.6661940625</v>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W124" s="4" t="n">
+        <v>46140.66803032407</v>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="19.2" customHeight="1">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>20260428-0005</t>
+        </is>
+      </c>
+      <c r="B125" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-Русе</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>23500</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="M125" s="3" t="n">
+        <v>15.31914893617021</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U125" s="4" t="n">
+        <v>46140.66811951389</v>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W125" s="4" t="n">
+        <v>46142.62504547454</v>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="19.2" customHeight="1">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>20260428-0006</t>
+        </is>
+      </c>
+      <c r="B126" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>НХК-Пчелник-Повеляново-Варна-Карапелит-Тервел-НХК</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>444</v>
+      </c>
+      <c r="M126" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U126" s="4" t="n">
+        <v>46140.66816375</v>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W126" s="4" t="n">
+        <v>46140.67040407407</v>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="19.2" customHeight="1">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>20260430-0001</t>
+        </is>
+      </c>
+      <c r="B127" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Варна-Ботево-Варна</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="M127" s="3" t="n">
+        <v>7.333333333333333</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U127" s="4" t="n">
+        <v>46142.62276876158</v>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W127" s="4" t="n">
+        <v>46142.6237709375</v>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
     </row>

--- a/transport/transport_data.xlsx
+++ b/transport/transport_data.xlsx
@@ -11760,6 +11760,2846 @@
         </is>
       </c>
     </row>
+    <row r="128" ht="19.2" customHeight="1">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>20260504-0001</t>
+        </is>
+      </c>
+      <c r="B128" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Русе-Тервел-Добрич-Ген. Киселово-Дългопол-Лукойл ПБ Аспарухово</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>384</v>
+      </c>
+      <c r="M128" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U128" s="4" t="n">
+        <v>46146.46505832176</v>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W128" s="4" t="n">
+        <v>46146.4661899537</v>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="19.2" customHeight="1">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>20260504-0002</t>
+        </is>
+      </c>
+      <c r="B129" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ПБ Лукойл Аспарухово - Енево - Повеляново- Любен Каравелово - Стожер-Добрич-Русе</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>34300</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>456</v>
+      </c>
+      <c r="M129" s="3" t="n">
+        <v>13.29446064139942</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U129" s="4" t="n">
+        <v>46146.46626918981</v>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W129" s="4" t="n">
+        <v>46146.46809652778</v>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="19.2" customHeight="1">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>20260504-0003</t>
+        </is>
+      </c>
+      <c r="B130" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Варна-Лукойл ПБ Аспарухово - Любен Каравелово - Кичево - Каварна - Варна</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="M130" s="3" t="n">
+        <v>18.33333333333333</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U130" s="4" t="n">
+        <v>46146.46818850694</v>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W130" s="4" t="n">
+        <v>46146.46899952546</v>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="19.2" customHeight="1">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>20260511-0001</t>
+        </is>
+      </c>
+      <c r="B131" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Русе-Тервел-Карапелит-Вълчи дол-Енево-Повеляново-Варна</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>384</v>
+      </c>
+      <c r="M131" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U131" s="4" t="n">
+        <v>46153.68160206018</v>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W131" s="4" t="n">
+        <v>46153.68275525463</v>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="19.2" customHeight="1">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>20260511-0002</t>
+        </is>
+      </c>
+      <c r="B132" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-Шумен-Русе</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="M132" s="3" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U132" s="4" t="n">
+        <v>46153.68284603009</v>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W132" s="4" t="n">
+        <v>46153.68436126158</v>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="19.2" customHeight="1">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>20260511-0003</t>
+        </is>
+      </c>
+      <c r="B133" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Долни Чифлик-Тервел-Кладенци-Карапелит-Варна</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>588</v>
+      </c>
+      <c r="M133" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U133" s="4" t="n">
+        <v>46153.68447539352</v>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W133" s="4" t="n">
+        <v>46153.68742084491</v>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="19.2" customHeight="1">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>20260511-0004</t>
+        </is>
+      </c>
+      <c r="B134" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-Каварна-Варна</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>37000</v>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="M134" s="3" t="n">
+        <v>6.486486486486486</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U134" s="4" t="n">
+        <v>46153.69973864583</v>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W134" s="4" t="n">
+        <v>46153.70183957176</v>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="19.2" customHeight="1">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>20260511-0005</t>
+        </is>
+      </c>
+      <c r="B135" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Варна-Девня-Варна</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>14600</v>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="M135" s="3" t="n">
+        <v>6.575342465753425</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U135" s="4" t="n">
+        <v>46153.70115335648</v>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W135" s="4" t="n">
+        <v>46153.70288130787</v>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="19.2" customHeight="1">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>20260515-0001</t>
+        </is>
+      </c>
+      <c r="B136" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Блъсково-Енево-Добрич-Каварна-Варна</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>588</v>
+      </c>
+      <c r="M136" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U136" s="4" t="n">
+        <v>46157.33152297453</v>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W136" s="4" t="n">
+        <v>46157.33366528935</v>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="19.2" customHeight="1">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>20260515-0002</t>
+        </is>
+      </c>
+      <c r="B137" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Варна-Повеляново-Варна</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="M137" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U137" s="4" t="n">
+        <v>46157.33371478009</v>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W137" s="4" t="n">
+        <v>46157.33469835648</v>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="19.2" customHeight="1">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>20260515-0003</t>
+        </is>
+      </c>
+      <c r="B138" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="M138" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U138" s="4" t="n">
+        <v>46157.33484365741</v>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W138" s="4" t="n">
+        <v>46157.33617449074</v>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="19.2" customHeight="1">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>20260518-0001</t>
+        </is>
+      </c>
+      <c r="B139" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Варна-Невестино-Тервел-Нова Камена-Карапелит-Повеляново-Варна</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="n">
+        <v>575</v>
+      </c>
+      <c r="K139" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>690</v>
+      </c>
+      <c r="M139" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U139" s="4" t="n">
+        <v>46160.62885799768</v>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W139" s="4" t="n">
+        <v>46160.63096947916</v>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="19.2" customHeight="1">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>20260519-0001</t>
+        </is>
+      </c>
+      <c r="B140" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Варна-Повеляново-Брестак-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>33500</v>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="M140" s="3" t="n">
+        <v>6.567164179104477</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U140" s="4" t="n">
+        <v>46161.45759795139</v>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W140" s="4" t="n">
+        <v>46161.46060762731</v>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="19.2" customHeight="1">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>20260519-0002</t>
+        </is>
+      </c>
+      <c r="B141" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Варна-Нефтохим-Добрич-Ген. Киселово-Повеляново-ЗПЗ-Варна</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="K141" s="2" t="n">
+        <v>30200</v>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>528</v>
+      </c>
+      <c r="M141" s="3" t="n">
+        <v>17.48344370860927</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U141" s="4" t="n">
+        <v>46161.46065765047</v>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W141" s="4" t="n">
+        <v>46164.4538156713</v>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="19.2" customHeight="1">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>20260519-0003</t>
+        </is>
+      </c>
+      <c r="B142" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Варна-Ботево-Енево-Аспарухово-Кладенци-Тервел-Варна</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="M142" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U142" s="4" t="n">
+        <v>46161.46238508102</v>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W142" s="4" t="n">
+        <v>46162.34453488426</v>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="19.2" customHeight="1">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>20260522-0001</t>
+        </is>
+      </c>
+      <c r="B143" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Варна-Каварна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K143" s="2" t="n">
+        <v>29600</v>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="M143" s="3" t="n">
+        <v>8.108108108108109</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U143" s="4" t="n">
+        <v>46164.45407395833</v>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W143" s="4" t="n">
+        <v>46164.45573337963</v>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="19.2" customHeight="1">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>20260528-0001</t>
+        </is>
+      </c>
+      <c r="B144" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>НХК-Каблешково-НХК</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>А1535ВВ</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K144" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="M144" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U144" s="4" t="n">
+        <v>46170.68285163194</v>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W144" s="4" t="n">
+        <v>46170.68494659722</v>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="19.2" customHeight="1">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>20260528-0002</t>
+        </is>
+      </c>
+      <c r="B145" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Нхк-Бургас-НХК</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>А1535ВВ</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K145" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="M145" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U145" s="4" t="n">
+        <v>46170.68406935185</v>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W145" s="4" t="n">
+        <v>46170.68573527778</v>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="19.2" customHeight="1">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>20260528-0003</t>
+        </is>
+      </c>
+      <c r="B146" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Варна-Каварна-Добрич-Повеляново-Варна</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>31600</v>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="M146" s="3" t="n">
+        <v>8.354430379746836</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U146" s="4" t="n">
+        <v>46170.68577809028</v>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W146" s="4" t="n">
+        <v>46170.68904938657</v>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="19.2" customHeight="1">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>20260528-0004</t>
+        </is>
+      </c>
+      <c r="B147" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Варна-Стожер-Добрич-Карапелит-Русе</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="M147" s="3" t="n">
+        <v>9.375</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U147" s="4" t="n">
+        <v>46170.68907090278</v>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W147" s="4" t="n">
+        <v>46170.69125917824</v>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="19.2" customHeight="1">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>20260528-0005</t>
+        </is>
+      </c>
+      <c r="B148" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Нхк-Енево-Тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="M148" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U148" s="4" t="n">
+        <v>46170.69134924769</v>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W148" s="4" t="n">
+        <v>46170.6927047338</v>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="19.2" customHeight="1">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>20260528-0007</t>
+        </is>
+      </c>
+      <c r="B149" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Добрич-Кипра-Варна</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="K149" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="M149" s="3" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U149" s="4" t="n">
+        <v>46170.69942094907</v>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W149" s="4" t="n">
+        <v>46170.70379078704</v>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="19.2" customHeight="1">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>20260528-0008</t>
+        </is>
+      </c>
+      <c r="B150" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Варна-Стожер-Варна</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K150" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="M150" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U150" s="4" t="n">
+        <v>46170.70191269676</v>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W150" s="4" t="n">
+        <v>46170.70265729167</v>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="19.2" customHeight="1">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>20260528-0009</t>
+        </is>
+      </c>
+      <c r="B151" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Варна-Неново-Блъсково-Варна</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="K151" s="2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="M151" s="3" t="n">
+        <v>13.35714285714286</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U151" s="4" t="n">
+        <v>46170.70270761574</v>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W151" s="4" t="n">
+        <v>46170.70430547454</v>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="19.2" customHeight="1">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>20260528-0010</t>
+        </is>
+      </c>
+      <c r="B152" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-Вълчи дол-Варна</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="K152" s="2" t="n">
+        <v>32800</v>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="M152" s="3" t="n">
+        <v>5.853658536585366</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U152" s="4" t="n">
+        <v>46170.70384761574</v>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W152" s="4" t="n">
+        <v>46170.70741564815</v>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="19.2" customHeight="1">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>20260529-0001</t>
+        </is>
+      </c>
+      <c r="B153" s="1" t="n">
+        <v>46165</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>ОФИС ПЛОВДИВ</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>НХК-соколово-котел</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>РОСБУЛ ТРАНС</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="M153" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U153" s="4" t="n">
+        <v>46171.37846791666</v>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W153" s="4" t="n">
+        <v>46171.37964732639</v>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="19.2" customHeight="1">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>20260529-0002</t>
+        </is>
+      </c>
+      <c r="B154" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>ОФИС ПЛОВДИВ</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>НХК - Просеник</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="M154" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U154" s="4" t="n">
+        <v>46171.37986307871</v>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W154" s="4" t="n">
+        <v>46171.38103491898</v>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="19.2" customHeight="1">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>20260602-0001</t>
+        </is>
+      </c>
+      <c r="B155" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Русе-Тервел-Карапелит-Добрич-НХК</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="M155" s="3" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>9500</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U155" s="4" t="n">
+        <v>46175.6936871875</v>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W155" s="4" t="n">
+        <v>46175.71441760417</v>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="19.2" customHeight="1">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>20260602-0002</t>
+        </is>
+      </c>
+      <c r="B156" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>НХК-Варна-Осем Ви -Русе</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>29000</v>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>444</v>
+      </c>
+      <c r="M156" s="3" t="n">
+        <v>15.31034482758621</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U156" s="4" t="n">
+        <v>46175.69703033565</v>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W156" s="4" t="n">
+        <v>46175.71482204861</v>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="19.2" customHeight="1">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>20260602-0003</t>
+        </is>
+      </c>
+      <c r="B157" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Варна-Каварна-Девня-Варна</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K157" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="M157" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="N157" s="2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U157" s="4" t="n">
+        <v>46175.69877569444</v>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W157" s="4" t="n">
+        <v>46175.71717149306</v>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="19.2" customHeight="1">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>20260602-0004</t>
+        </is>
+      </c>
+      <c r="B158" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Варна-Повеляново-Тервел-Варна</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="M158" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U158" s="4" t="n">
+        <v>46175.71488966435</v>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W158" s="4" t="n">
+        <v>46175.7166493287</v>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
